--- a/public/templates/office/EMP_DEG_030_정책정의서.xlsx
+++ b/public/templates/office/EMP_DEG_030_정책정의서.xlsx
@@ -3292,7 +3292,7 @@
       </c>
       <c r="C12" s="164" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="203" t="n"/>
@@ -3347,7 +3347,7 @@
     <row r="22" ht="18.75" customHeight="1" s="202">
       <c r="C22" s="206" t="inlineStr">
         <is>
-          <t>그로브소프트 (EMPASY)</t>
+          <t>엠파시 (EMPASY)</t>
         </is>
       </c>
       <c r="D22" s="207" t="n"/>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t>BO ALB(사용자대역 오픈) / 대외연계 ALB(티움넷 서버만 오픈) 물리 분리 정책, BO·대외연계 서버의 EKS Service 기반 AI Agent 호출 정책, AI 피크프레임 1차 자동추출 + 웹 동영상 재생 기반 장면 추가/편집/삭제 보정 정책, S3 Intelligent-Tiering 자동 적용 및 AP 기본 제공 스펙 정책 반영</t>
+          <t>BO ALB(사용자대역 오픈) / 대외연계 ALB(마케팅허브 서버만 오픈) 물리 분리 정책, BO·대외연계 서버의 EKS Service 기반 AI Agent 호출 정책, AI 피크프레임 1차 자동추출 + 웹 동영상 재생 기반 장면 추가/편집/삭제 보정 정책, S3 Intelligent-Tiering 자동 적용 및 AP 기본 제공 스펙 정책 반영</t>
         </is>
       </c>
       <c r="E6" s="44" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="E6" s="227" t="inlineStr">
         <is>
-          <t>화장품법 제13조 및 식약처 가이드라인 엄격 준수</t>
+          <t>표시·광고 공정화법 제3조 및 식약처 가이드라인 엄격 준수</t>
         </is>
       </c>
       <c r="F6" s="226" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="E8" s="227" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 정보보안센터 보안성 검토 승인 완료 요건</t>
+          <t>한빛글로벌 정보보안센터 보안성 검토 승인 완료 요건</t>
         </is>
       </c>
       <c r="F8" s="226" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="D10" s="227" t="inlineStr">
         <is>
-          <t>1. 대외 연계 전용 ALB(syncguard-ai-api-prv-alb) &amp; 대외 연계 서버(server-api :18085): 티움넷(MarketingHub) 서버 IP 대역만 오픈하여 접근을 통제하며, 심의 의뢰 접수·300MB 파일 S3 업로드·결과 회신 및 EKS Service를 통한 AI Agent 호출 수행
+          <t>1. 대외 연계 전용 ALB(syncguard-ai-api-prv-alb) &amp; 대외 연계 서버(server-api :18085): 마케팅허브(MarketingHub) 서버 IP 대역만 오픈하여 접근을 통제하며, 심의 의뢰 접수·300MB 파일 S3 업로드·결과 회신 및 EKS Service를 통한 AI Agent 호출 수행
 2. BO 전용 ALB(syncguard-ai-bo-prv-alb) &amp; 통합 웹(:3104)·업무 서버(server-be :18080): 사내 사용자 PC/VPN 대역만 오픈하며, 사내 IAM 권한 검증(validateBoAdminPermission) 기반 심의·웹 영상 장면 보정·백오피스 운영 및 EKS Service를 통한 AI Agent 호출 수행
 3. BO ALB와 대외 연계 ALB를 물리적으로 분리하여 네트워크 수준에서 접근 권한을 엄격히 통제</t>
         </is>
@@ -4310,7 +4310,7 @@
       <c r="D13" s="227" t="inlineStr">
         <is>
           <t>1. AI Agent 동시 분석 제어 및 EKS Service 호출: 동시 분석 건수를 최대 4건(Semaphore)으로 제한(초과 시 QUEUED 대기열 폴링)하며, 대외 연계 서버(:18085)와 BO 업무 서버(:18080) 모두 EKS K8s Service(http://syncguard-ai-agent-svc:18083)를 통해 AI Agent를 호출
-2. 인프라 스펙 운영: 초기 인프라는 아모레퍼시픽(AP) 기본 제공 타입으로 구성하며, 성능 테스트 시 OOM 등 리소스 부족 현상으로 서비스가 중단되는 이슈가 지속 발생하는 시점에 스펙 증설 요청</t>
+2. 인프라 스펙 운영: 초기 인프라는 한빛글로벌(AP) 기본 제공 타입으로 구성하며, 성능 테스트 시 심의M 등 리소스 부족 현상으로 서비스가 중단되는 이슈가 지속 발생하는 시점에 스펙 증설 요청</t>
         </is>
       </c>
       <c r="E13" s="227" t="inlineStr">

--- a/public/templates/office/EMP_DEG_030_정책정의서.xlsx
+++ b/public/templates/office/EMP_DEG_030_정책정의서.xlsx
@@ -3292,7 +3292,7 @@
       </c>
       <c r="C12" s="164" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="203" t="n"/>
@@ -3353,7 +3353,7 @@
       <c r="D22" s="207" t="n"/>
       <c r="E22" s="208" t="inlineStr">
         <is>
-          <t>고객사명</t>
+          <t>주식회사 한빛글로벌</t>
         </is>
       </c>
       <c r="F22" s="209" t="n"/>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D4" s="216" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" s="216" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D5" s="43" t="inlineStr">
         <is>
-          <t>FO/BO 권한 분리(IAM BO 권한 검증), 네이버/패들 OCR 설정 선택 정책, AI Agent 동시 4건 대기열(QUEUED) 및 수동 재실행 정책 반영</t>
+          <t>FO/BO 권한 분리(IAM BO 권한 검증), 엔터프라이즈 멀티모달 OCR 설정 선택 정책, AI Agent 동시 4건 대기열(QUEUED) 및 수동 재실행 정책 반영</t>
         </is>
       </c>
       <c r="E5" s="44" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t>BO ALB(사용자대역 오픈) / 대외연계 ALB(마케팅허브 서버만 오픈) 물리 분리 정책, BO·대외연계 서버의 EKS Service 기반 AI Agent 호출 정책, AI 피크프레임 1차 자동추출 + 웹 동영상 재생 기반 장면 추가/편집/삭제 보정 정책, S3 Intelligent-Tiering 자동 적용 및 AP 기본 제공 스펙 정책 반영</t>
+          <t>BO ALB(사용자대역 오픈) / 대외연계 ALB(전자구매포털 서버만 오픈) 물리 분리 정책, BO·대외연계 서버의 EKS Service 기반 AI Agent 호출 정책, AI 도면스냅샷 1차 자동추출 + 웹 설계도면 재생 기반 장면 추가/편집/삭제 보정 정책, S3 Intelligent-Tiering 자동 적용 및 HB 표준 제공 스펙 정책 반영</t>
         </is>
       </c>
       <c r="E6" s="44" t="inlineStr">
@@ -3811,7 +3811,7 @@
     <row r="5">
       <c r="A5" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-001</t>
+          <t>POL-REV-001</t>
         </is>
       </c>
       <c r="B5" s="226" t="inlineStr">
@@ -3827,13 +3827,13 @@
       <c r="D5" s="227" t="inlineStr">
         <is>
           <t>1. 1단계: 사전 등록된 금지 표현 룰 매칭 즉시 차단(정밀도 100%)
-2. 2단계: 식약처 행정처분 및 규제 판례 RAG 검색을 통한 유사도 기반 주의/실증 요구 판정
-3. 3단계: 전체 문맥 및 수식어 조합을 반영한 LLM Agent 심의(안전/권고)</t>
+2. 2단계: 공정위·표준원 시정명령·심결 및 규제 판례 RAG 검색을 통한 유사도 기반 주의/시험검증 요구 판정
+3. 3단계: 전체 문맥 및 수식어 조합을 반영한 LLM Agent 검증(안전/권고)</t>
         </is>
       </c>
       <c r="E5" s="227" t="inlineStr">
         <is>
-          <t>AI 결과는 검토를 돕는 권고안이며, 최종 판정은 RA 전문가가 확정함</t>
+          <t>AI 결과는 검토를 돕는 권고안이며, 최종 판정은 법무·QA 전문위원가 확정함</t>
         </is>
       </c>
       <c r="F5" s="228" t="inlineStr">
@@ -3872,28 +3872,28 @@
     <row r="6">
       <c r="A6" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-002</t>
+          <t>POL-REV-002</t>
         </is>
       </c>
       <c r="B6" s="226" t="inlineStr">
         <is>
-          <t>표시광고</t>
+          <t>계약·기술규격</t>
         </is>
       </c>
       <c r="C6" s="227" t="inlineStr">
         <is>
-          <t>의약품 오인 우려 표현 절대 금지 정책</t>
+          <t>불공정 독소조항 우려 표현 절대 금지 정책</t>
         </is>
       </c>
       <c r="D6" s="227" t="inlineStr">
         <is>
-          <t>1. '치료', '재생', '완치', '염증 완화', '피부 재생' 등 질병 치료 및 의학적 효능 표현은 무조건 '금지(BAN)' 판정
-2. 단순 피부결 개선이나 보습 효과와 명확히 구분하여 필터링</t>
+          <t>1. '면책', '재생', '전가', '부식 완화', '전장부품 재생' 등 일방 면책 및 의학적 성능규격 표현은 무조건 '금지(BAN)' 판정
+2. 단순 납품일정 개선이나 내열성 효과와 명확히 구분하여 필터링</t>
         </is>
       </c>
       <c r="E6" s="227" t="inlineStr">
         <is>
-          <t>표시·광고 공정화법 제3조 및 식약처 가이드라인 엄격 준수</t>
+          <t>하도급법 제3조의4 및 공정위·표준원 가이드라인 엄격 준수</t>
         </is>
       </c>
       <c r="F6" s="226" t="inlineStr">
@@ -3932,28 +3932,28 @@
     <row r="7">
       <c r="A7" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-003</t>
+          <t>POL-REV-003</t>
         </is>
       </c>
       <c r="B7" s="226" t="inlineStr">
         <is>
-          <t>실증검증</t>
+          <t>시험검증검증</t>
         </is>
       </c>
       <c r="C7" s="227" t="inlineStr">
         <is>
-          <t>효능·효과 수치 및 지속시간 실증자료 연동 정책</t>
+          <t>성능·규격 수치 및 지속시간 시험성적서 연동 정책</t>
         </is>
       </c>
       <c r="D7" s="227" t="inlineStr">
         <is>
-          <t>1. '72시간 보습 지속', '주름 30% 개선' 등 구체적 수치나 지속시간 표현은 '주의(CAUTION)' 판정
-2. ProductLab 실증자료(임상시험 성적서) 매핑이 완료되어야 '안전' 승인 가능</t>
+          <t>1. '2,000시간 내열·진동 보증', '내진동 30% 개선' 등 구체적 수치나 지속시간 표현은 '주의(CAUTION)' 판정
+2. PLM-Nexus 시험성적서(신뢰성시험 성적서) 매핑이 완료되어야 '안전' 승인 가능</t>
         </is>
       </c>
       <c r="E7" s="227" t="inlineStr">
         <is>
-          <t>실증자료 번호 매핑 및 유효기간 만료 여부 자동 점검</t>
+          <t>시험성적서 번호 매핑 및 유효기간 만료 여부 자동 점검</t>
         </is>
       </c>
       <c r="F7" s="226" t="inlineStr">
@@ -3992,7 +3992,7 @@
     <row r="8">
       <c r="A8" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-004</t>
+          <t>POL-REV-004</t>
         </is>
       </c>
       <c r="B8" s="226" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="D8" s="227" t="inlineStr">
         <is>
-          <t>1. 외부 LLM API(Anthropic, OpenAI 등) 호출 시 모든 시안 문안 및 프롬프트는 비학습 조건 계약 적용
+          <t>1. 외부 LLM API(Anthropic, OpenAI 등) 호출 시 모든 계약·도서 계약조항 및 프롬프트는 비학습 조건 계약 적용
 2. 전송 구간 TLS 1.3 암호화 및 개인정보/사내 대외비 마스킹 처리</t>
         </is>
       </c>
@@ -4052,7 +4052,7 @@
     <row r="9">
       <c r="A9" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-005</t>
+          <t>POL-REV-005</t>
         </is>
       </c>
       <c r="B9" s="226" t="inlineStr">
@@ -4062,18 +4062,18 @@
       </c>
       <c r="C9" s="227" t="inlineStr">
         <is>
-          <t>심의 확정 데이터 불변성(Immutable) 보존 정책</t>
+          <t>검증 확정 데이터 불변성(Immutable) 보존 정책</t>
         </is>
       </c>
       <c r="D9" s="227" t="inlineStr">
         <is>
-          <t>1. RA 최종 확정 시 원본 시안 파일, 추출 문장, AI 판정 결과, RA 의견을 review_history_immutable에 저장
+          <t>1. QA 최종 확정 시 원본 계약·도서 파일, 추출 문장, AI 판정 결과, QA 의견을 verify_history_immutable에 저장
 2. 저장된 감사 테이블은 UPDATE/DELETE 권한을 전면 차단하여 위변조 방지</t>
         </is>
       </c>
       <c r="E9" s="227" t="inlineStr">
         <is>
-          <t>식약처 사후 소명 시 원본 증적 자료로 활용</t>
+          <t>공정위·표준원 사후 소명 시 원본 증적 자료로 활용</t>
         </is>
       </c>
       <c r="F9" s="226" t="inlineStr">
@@ -4112,7 +4112,7 @@
     <row r="10">
       <c r="A10" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-006</t>
+          <t>POL-REV-006</t>
         </is>
       </c>
       <c r="B10" s="226" t="inlineStr">
@@ -4127,14 +4127,14 @@
       </c>
       <c r="D10" s="227" t="inlineStr">
         <is>
-          <t>1. 대외 연계 전용 ALB(syncguard-ai-api-prv-alb) &amp; 대외 연계 서버(server-api :18085): 마케팅허브(MarketingHub) 서버 IP 대역만 오픈하여 접근을 통제하며, 심의 의뢰 접수·300MB 파일 S3 업로드·결과 회신 및 EKS Service를 통한 AI Agent 호출 수행
-2. BO 전용 ALB(syncguard-ai-bo-prv-alb) &amp; 통합 웹(:3104)·업무 서버(server-be :18080): 사내 사용자 PC/VPN 대역만 오픈하며, 사내 IAM 권한 검증(validateBoAdminPermission) 기반 심의·웹 영상 장면 보정·백오피스 운영 및 EKS Service를 통한 AI Agent 호출 수행
+          <t>1. 대외 연계 전용 ALB(syncflow-ai-api-prv-alb) &amp; 대외 연계 서버(server-api :18085): 전자구매포털(SRM-Portal) 서버 IP 대역만 오픈하여 접근을 통제하며, 검증 요청 접수·300MB 파일 S3 업로드·결과 회신 및 EKS Service를 통한 AI Agent 호출 수행
+2. BO 전용 ALB(syncflow-ai-bo-prv-alb) &amp; 통합 웹(:3104)·업무 서버(server-be :18080): 사내 사용자 PC/VPN 대역만 오픈하며, 사내 IAM 권한 검증(validateBoAdminPermission) 기반 검증·웹 영상 장면 보정·백오피스 운영 및 EKS Service를 통한 AI Agent 호출 수행
 3. BO ALB와 대외 연계 ALB를 물리적으로 분리하여 네트워크 수준에서 접근 권한을 엄격히 통제</t>
         </is>
       </c>
       <c r="E10" s="227" t="inlineStr">
         <is>
-          <t>사내 SSO 로그인 세션 및 JWT 역할 클레임 연동</t>
+          <t>사내 SSO 로그인 세션 및 JWT 역할 규격·계약 연동</t>
         </is>
       </c>
       <c r="F10" s="226" t="inlineStr">
@@ -4173,23 +4173,23 @@
     <row r="11">
       <c r="A11" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-007</t>
+          <t>POL-REV-007</t>
         </is>
       </c>
       <c r="B11" s="226" t="inlineStr">
         <is>
-          <t>문안교정</t>
+          <t>계약조항교정</t>
         </is>
       </c>
       <c r="C11" s="227" t="inlineStr">
         <is>
-          <t>사내 승인 문구 우선 추천 정책</t>
+          <t>사내 승인 조항 우선 추천 정책</t>
         </is>
       </c>
       <c r="D11" s="227" t="inlineStr">
         <is>
-          <t>1. 금지/주의 표현 감지 시 AI 임의 생성 문구보다 사내 마스터 표현 사전에 등록된 검증된 '권장 대체 문구' 1순위 추천
-2. 마케터가 One-Click으로 원본 시안 텍스트 교체 가능하도록 지원</t>
+          <t>1. 금지/주의 표현 감지 시 AI 임의 생성 조항보다 사내 마스터 표현 사전에 등록된 검증된 '권장 대체 조항' 1순위 추천
+2. 구매담당자가 One-Click으로 원본 계약·도서 텍스트 교체 가능하도록 지원</t>
         </is>
       </c>
       <c r="E11" s="227" t="inlineStr">
@@ -4233,29 +4233,29 @@
     <row r="12">
       <c r="A12" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-008</t>
+          <t>POL-REV-008</t>
         </is>
       </c>
       <c r="B12" s="226" t="inlineStr">
         <is>
-          <t>시안검증</t>
+          <t>계약·도서검증</t>
         </is>
       </c>
       <c r="C12" s="227" t="inlineStr">
         <is>
-          <t>선택형 OCR, 동영상 1차 AI 피크프레임 추출·2차 웹 장면 보정 및 S3 Intelligent-Tiering 정책</t>
+          <t>선택형 OCR, 설계도면 1차 AI 도면 규격영역 추출·2차 웹 장면 보정 및 S3 Intelligent-Tiering 정책</t>
         </is>
       </c>
       <c r="D12" s="227" t="inlineStr">
         <is>
-          <t>1. OCR 엔진 설정 선택: claim.ocr.provider 설정(NAVER | PADDLE | AUTO)을 통해 네이버 클로바 OCR(https://*.apigw.ntruss.com)과 패들 OCR을 선택 운영
-2. 동영상(MP4) 2단계 처리: 1차로 AI Agent가 OpenCV로 영상 피크프레임을 자동 추출하고, 이후 이를 보정하기 위해 통합 웹 화면(:3104)에서 동영상을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제한 뒤 BO 서버(:18080)에서 AI Agent(:18083)로 재분석 요청
+          <t>1. OCR 엔진 설정 선택: Spec.ocr.provider 설정(NAVER | PADDLE | AUTO)을 통해 엔터프라이즈 비전 OCR(https://ocr-api.hanbitglobal.internal)과 도면 OCR을 선택 운영
+2. 설계도면(CAD/PDF) 2단계 처리: 1차로 AI Agent가 OpenCV로 영상 도면스냅샷을 자동 추출하고, 이후 이를 보정하기 위해 통합 웹 화면(:3104)에서 설계도면을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제한 뒤 BO 서버(:18080)에서 AI Agent(:18083)로 재분석 요청
 3. S3 Intelligent-Tiering 자동 적용: 파일 보관주기가 미확정됨에 따라 S3 업로드 시 파일 저장 타입을 'Intelligent-Tiering'으로 자동 지정하여 자동 패턴 분석 기반 보관비용 관리</t>
         </is>
       </c>
       <c r="E12" s="227" t="inlineStr">
         <is>
-          <t>비정형 시안 오인식에 따른 판정 누락 방지</t>
+          <t>비정형 계약·도서 오인식에 따른 판정 누락 방지</t>
         </is>
       </c>
       <c r="F12" s="226" t="inlineStr">
@@ -4294,7 +4294,7 @@
     <row r="13">
       <c r="A13" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-009</t>
+          <t>POL-REV-009</t>
         </is>
       </c>
       <c r="B13" s="226" t="inlineStr">
@@ -4304,13 +4304,13 @@
       </c>
       <c r="C13" s="227" t="inlineStr">
         <is>
-          <t>AI Agent 동시 4건 대기열 제어, EKS Service 통신 및 AP 기본 인프라 스펙 운영 정책</t>
+          <t>AI Agent 동시 4건 대기열 제어, EKS Service 통신 및 HB 표준 인프라 스펙 운영 정책</t>
         </is>
       </c>
       <c r="D13" s="227" t="inlineStr">
         <is>
-          <t>1. AI Agent 동시 분석 제어 및 EKS Service 호출: 동시 분석 건수를 최대 4건(Semaphore)으로 제한(초과 시 QUEUED 대기열 폴링)하며, 대외 연계 서버(:18085)와 BO 업무 서버(:18080) 모두 EKS K8s Service(http://syncguard-ai-agent-svc:18083)를 통해 AI Agent를 호출
-2. 인프라 스펙 운영: 초기 인프라는 한빛글로벌(AP) 기본 제공 타입으로 구성하며, 성능 테스트 시 심의M 등 리소스 부족 현상으로 서비스가 중단되는 이슈가 지속 발생하는 시점에 스펙 증설 요청</t>
+          <t>1. AI Agent 동시 분석 제어 및 EKS Service 호출: 동시 분석 건수를 최대 4건(Semaphore)으로 제한(초과 시 QUEUED 대기열 폴링)하며, 대외 연계 서버(:18085)와 BO 업무 서버(:18080) 모두 EKS K8s Service(http://syncflow-ai-agent-svc:18083)를 통해 AI Agent를 호출
+2. 인프라 스펙 운영: 초기 인프라는 한빛글로벌(AP) 기본 제공 타입으로 구성하며, 성능 테스트 시 검증M 등 리소스 부족 현상으로 서비스가 중단되는 이슈가 지속 발생하는 시점에 스펙 증설 요청</t>
         </is>
       </c>
       <c r="E13" s="227" t="inlineStr">
@@ -4354,7 +4354,7 @@
     <row r="14">
       <c r="A14" s="226" t="inlineStr">
         <is>
-          <t>POL-CLM-010</t>
+          <t>POL-REV-010</t>
         </is>
       </c>
       <c r="B14" s="226" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="D14" s="227" t="inlineStr">
         <is>
-          <t>1. 식약처 가이드라인 개정 또는 AI 프롬프트 튜닝 시 100건의 과거 심의 정답셋으로 자동 회귀 평가
+          <t>1. 공정위·표준원 가이드라인 개정 또는 AI 프롬프트 튜닝 시 100건의 과거 검증 정답셋으로 자동 회귀 평가
 2. 판정 정밀도(Precision)가 90% 이상 달성되어야만 신규 프롬프트 배포 승인</t>
         </is>
       </c>
